--- a/www/download/IND.gross_output.s.du.WIOD13.xlsx
+++ b/www/download/IND.gross_output.s.du.WIOD13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>135327.91497024</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>138663.401584926</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137743.106025924</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>136924.734008715</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151297.653602737</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>148745.138532922</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>140409.779799281</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>150882.871692452</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>170355.068158554</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>209835.387235671</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>229724.925316366</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>244824.875682117</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>290745.376333556</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>337015.416540577</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>321200.032612685</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72752.3610298521</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75315.5571608565</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>69933.9870213347</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>71219.009978881</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>73844.7661572102</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79673.0520424066</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78778.553662458</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78387.7341993598</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>87333.6896260929</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>99419.0118698319</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105027.568352207</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>118663.178474376</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>138025.875617739</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>140880.907593321</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112342.394944382</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>91832.7392740208</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>87347.6381131839</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82590.9818304017</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83524.6889415128</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88066.990650333</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98019.1394396157</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95209.8107929586</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>94266.9135776621</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>109507.383792793</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>128356.182581801</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>132346.564258839</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>149461.839488098</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>175827.846172081</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>227010.119117819</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>158838.235159117</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59975.7202726541</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63566.2502206878</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57496.9481985903</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54342.3234858351</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52915.060881566</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50810.9223009569</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47697.0129847994</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47678.4858225798</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52959.619181942</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62254.9673788653</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68276.4862631004</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>75945.6102312475</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>88841.8219565254</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98695.6535597433</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>92044.7546301741</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1235325.3829822</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>1225836.26928535</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.213</t>
+          <t>1212621.12021768</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.177</t>
+          <t>1176750.43564102</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>1259273.67722923</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1316922.00341994</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1249632.98049125</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.323</t>
+          <t>1323096.46755483</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1464675.51610275</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.697</t>
+          <t>1697272.52129371</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.855</t>
+          <t>1855293.31342445</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1916793.62157408</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.192</t>
+          <t>2191568.88707868</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.486</t>
+          <t>2486072.55572423</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.237</t>
+          <t>2236919.27404345</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>214304.90980031</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>219805.486805602</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>216393.290595869</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>217569.133046026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>241700.511758091</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>268886.765897669</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>263468.803400609</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>259339.185639423</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>290563.615804625</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>350490.797740458</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>385682.737143778</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>416278.295088123</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>456013.296042383</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>511430.979031091</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>438507.401565638</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15.125</t>
+          <t>15126263.1888326</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15.649</t>
+          <t>15649342.3790846</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15.641</t>
+          <t>15641143.9338876</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15.389</t>
+          <t>15389253.9399697</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15.823</t>
+          <t>15907822.7321883</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>15.911</t>
+          <t>15911266.108939</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15.734</t>
+          <t>15734730.1684648</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16.356</t>
+          <t>16356710.9121391</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>18.636</t>
+          <t>18636486.0613312</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>21.033</t>
+          <t>21033585.3889652</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>23.689</t>
+          <t>23688938.3489101</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>27.241</t>
+          <t>27240116.9964364</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>32.121</t>
+          <t>32121699.8980419</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>36.955</t>
+          <t>36954630.0954668</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>34.932</t>
+          <t>34930683.3020388</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4692.37759154638</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5166.89700537609</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4550.42831800548</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4573.97989983913</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5210.05213847406</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5215.40836282184</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5609.28864053445</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5910.79029674408</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6608.28794648945</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6922.25532823096</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6750.32823477782</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7267.19004576828</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7939.57043878493</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12186.9312881208</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7513.37510620318</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105389.076500301</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108808.533487822</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110596.438650563</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105351.562316628</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>103953.260943664</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103029.290189538</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102841.583682191</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>106278.916820354</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113924.864804174</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>128767.466358829</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137815.932661298</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>155227.949523824</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>182465.958222814</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>195184.811652445</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151089.589956127</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>669451.568186757</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>623953.118608015</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>588507.246597533</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>609155.156407885</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>635428.236024096</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>688727.734481068</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>640417.339279158</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>632027.827028679</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>725651.944537071</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.835</t>
+          <t>836220.926547088</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>884304.278751002</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.981</t>
+          <t>980593.589189179</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.162</t>
+          <t>1160557.68192883</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1150285.01643258</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>893555.777012299</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55870.0233445572</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55766.9862771174</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>58262.0679184369</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53210.37480043</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51579.4094448821</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53659.1679626388</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53507.2232963952</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53548.6245387652</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>61199.8668963427</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>68981.7001479665</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72183.2171556246</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77225.2081363318</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89233.851264998</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>91364.5043217491</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72324.0497200934</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>255186.702959497</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>257282.274742876</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>244485.759835964</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>259350.148962446</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>290440.495661462</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>320510.713519807</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>316056.518017661</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>339138.418143346</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>374413.043492256</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>433067.79880086</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>484745.440191125</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>529796.195134355</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>615313.427674566</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>639017.566043233</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>470941.886386106</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11147.6793270204</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10855.9328210472</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11256.3017833092</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11402.1885284278</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10958.2860872872</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12098.3423123363</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12736.3824002911</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13676.5001623141</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15626.1210763378</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18346.5318184203</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18172.889064758</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19515.3709498958</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20540.1124513495</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21793.417582923</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16518.3716721394</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52171.2900189424</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51594.659732165</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50048.3189249447</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52941.3858156729</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57612.6734373237</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59850.0549457503</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55791.1127828388</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56368.0786873539</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63859.9759470227</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72325.5097064988</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79936.4584333848</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87734.4862637216</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>101008.347287382</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>104797.097853347</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72365.7526820152</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>380403.158742082</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>374348.771092966</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>339361.750196716</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>350102.064572402</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>384332.754169121</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>407156.082705889</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>394058.140722466</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>389743.779477992</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>437018.849035085</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>496796.357425596</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>538379.471626477</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>571405.128133885</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.665</t>
+          <t>664495.67265904</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>682318.843358693</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>557719.89260326</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>402084.699166096</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>410090.220355435</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>391552.404748227</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>388104.540171271</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>397649.049526667</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>402014.496986547</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>383694.195263882</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>382537.406438272</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>416923.170793829</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>476787.204239014</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>520905.413116193</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>551259.775700031</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>624056.905438893</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>613548.828702514</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.513</t>
+          <t>513101.940705768</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76464.0009730254</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79149.0738316439</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72434.3423380638</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71707.6128528388</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>73935.4064216951</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82674.0146200357</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76544.4300149648</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78253.3672315703</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83957.0911168921</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>90548.6241105429</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96960.0396009292</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108739.439619075</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>123520.976349675</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137583.660968069</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>117064.549252612</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83185.0618610599</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82975.3505239504</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78760.4741374101</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79871.2260249638</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89895.883134102</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>90147.3636639411</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>85282.0673054651</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>86922.44052074</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>93418.863966988</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97401.2649086488</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102749.040295218</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108174.798255454</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>125167.399813963</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123306.754627323</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102817.893852472</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>1093096.95191189</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.143</t>
+          <t>1143034.74349424</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.103</t>
+          <t>1103463.4780083</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1029605.15891757</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1202123.68957088</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.313</t>
+          <t>1313065.43994247</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.308</t>
+          <t>1307823.05491384</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.424</t>
+          <t>1423794.07991958</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1588030.8500131</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.733</t>
+          <t>1732660.28673479</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1647760.40839499</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>1667333.26795812</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.963</t>
+          <t>1962741.45175041</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2220077.44753859</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.181</t>
+          <t>2180699.82539028</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9.305</t>
+          <t>9305322.79285708</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>9.517</t>
+          <t>9517253.82047162</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>9.605</t>
+          <t>9605415.81201386</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>9.492</t>
+          <t>9492402.29051717</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>9.607</t>
+          <t>9581198.09403641</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>10.196</t>
+          <t>10195822.8087659</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10.265</t>
+          <t>10265598.4825184</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>10.268</t>
+          <t>10268928.8328253</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>11.905</t>
+          <t>11906048.5547785</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>13.397</t>
+          <t>13397138.3987929</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>14.644</t>
+          <t>14644572.2379602</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>15.509</t>
+          <t>15508890.1847291</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>17.102</t>
+          <t>17102686.1757854</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>18.798</t>
+          <t>18798957.9844014</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>17.932</t>
+          <t>17931413.1288934</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34648.6724990571</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35725.2186789691</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34600.6924241979</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34139.1297923403</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38939.6680888424</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42353.7779613867</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42103.8595239261</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40725.9569198131</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46722.7445668636</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56466.4070068507</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63597.4617780962</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69404.4573966809</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>82032.3033229718</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79177.8868355544</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64974.3237033251</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>459049.309874514</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>460110.384223097</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>433903.840325025</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>446266.890128789</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>463638.084567734</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>504774.495525646</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>489248.596221665</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>495955.492769561</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>555853.410229392</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>639100.270792363</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>676424.266730454</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>759671.43915598</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>866185.264210364</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.853</t>
+          <t>852528.495792308</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>644982.853959285</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.592</t>
+          <t>1590412.49421054</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1527917.90310147</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1461017.99430422</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.312</t>
+          <t>1312196.94920132</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.393</t>
+          <t>1375644.04164693</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1494345.13101732</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1395563.9700403</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.361</t>
+          <t>1359144.60952565</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.519</t>
+          <t>1516946.07671827</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.757</t>
+          <t>1754684.27334266</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1.883</t>
+          <t>1881026.81750942</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2.027</t>
+          <t>2029607.56915201</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2.268</t>
+          <t>2267087.30006851</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2608134.69777946</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2.054</t>
+          <t>2057138.40922012</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>644915.771121175</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>651792.438503643</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>635973.608593673</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>538967.475975637</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>612640.26830685</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>669287.993048738</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>633334.354798539</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>659585.298803112</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>732811.780791009</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>872670.482822036</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>935443.708401949</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1.028</t>
+          <t>1028118.66801933</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1164892.09135486</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1328003.31037595</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.136</t>
+          <t>1135792.79695094</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25303.5624392483</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24860.3538177967</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22233.4131260765</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23589.0248068368</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22999.7354385118</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24191.2640755026</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23118.9318246348</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23950.868788087</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26688.4646590408</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27918.7576705991</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31471.9647338157</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32593.8384039458</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37567.1198198339</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43729.1658977062</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34993.4118774488</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3757.71408733854</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3362.90098530754</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3137.21336998143</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3366.64919580425</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3378.59895231064</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3683.79892469742</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3451.37568129863</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3542.92210226164</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4360.33086167453</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5424.06098506898</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5904.16399841468</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6423.87746227593</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7226.05333927348</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8219.28622811915</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7028.22369420314</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12016.8651029845</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11822.4288371108</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11874.4973236408</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12033.4777598487</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11902.7165765914</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10881.334160338</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10513.898554263</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10699.8278127725</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12489.9381249448</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14895.6618022158</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16538.4879348116</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18644.9485992324</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23514.5444042293</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23359.9249121739</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15742.3420105281</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>538219.550592529</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>569098.947994702</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>558950.289277258</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>588551.911806249</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>637478.118337901</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.675</t>
+          <t>674995.743729437</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>671634.869015428</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>679559.291982785</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>746284.1488434</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.863</t>
+          <t>862619.174185916</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.933</t>
+          <t>933407.316808614</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>979590.681059752</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.095</t>
+          <t>1095027.78602666</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1294472.16993067</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.173</t>
+          <t>1172732.80084604</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2396.56768897382</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2402.0968434955</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2068.35333822455</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2205.66307257811</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2579.62665579798</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2964.21129143372</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2389.61038449804</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2554.42747198595</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2779.81171056157</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2906.15389302161</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2919.17215530772</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3392.53602197156</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3851.46308656329</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4342.9334709808</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3532.53390638339</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171860.81745026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>176005.936376674</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>162242.129196153</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>177890.049225528</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>194425.695981611</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>196997.339086254</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>197636.595282004</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171032.922363387</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>224207.024761699</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>252098.405803249</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>279363.537196738</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>292013.945680905</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>347992.654915652</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>391083.504746072</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>316554.664736887</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>296040.146138956</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>304180.729236139</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>295343.565730152</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>293086.067925434</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>288569.295238013</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>301245.784882972</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>256137.686363847</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>246469.088513254</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>264125.763143501</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>299675.483862755</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>330625.240301026</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>361399.33893826</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>437199.230410751</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>478059.548683649</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>401817.433007954</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>96301.0035120527</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>95972.0218747048</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>90061.575232996</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>94019.2637477182</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97054.9399248016</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>105887.127887413</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103116.246557445</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102806.73509387</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109071.706116638</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>122692.65443</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>126440.805850134</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>132174.414171177</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>153924.432319899</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>172268.841074442</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129653.194424245</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>216565.320438449</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>229339.743971805</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>202661.274363581</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>185137.105172297</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>236906.264511618</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>234070.69337979</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>225666.599338366</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>199717.761240696</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>211485.505238291</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>223267.691493959</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>234807.483281508</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>245513.66740045</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>282454.098403047</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>314085.198789581</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>278648.322286676</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.438</t>
+          <t>1437663.08969651</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1456680.33056025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.359</t>
+          <t>1358575.25508065</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.274</t>
+          <t>1274213.66557413</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.236</t>
+          <t>1223635.1238873</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.297</t>
+          <t>1296537.54131909</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.294</t>
+          <t>1293925.32555061</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1284742.25691478</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.388</t>
+          <t>1388247.16430465</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1510386.32359082</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1616343.03485862</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.657</t>
+          <t>1657000.01796899</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.956</t>
+          <t>1955804.89989342</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2.184</t>
+          <t>2184606.68309562</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.995</t>
+          <t>1994531.15097136</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42329.2705605839</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43629.8243618158</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39809.4806563929</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38602.1265203063</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38379.8443066433</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38173.4590428798</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37539.5851915402</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36976.8325027409</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41296.5023121714</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46292.7549323951</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51684.4470045501</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57675.370285806</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72821.1239808487</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81905.4816961072</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71971.9769264677</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19918.8719320711</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19472.844603088</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18027.2999498839</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18150.4744140514</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18898.8949085704</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19888.54872421</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19440.8072442455</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19705.4719771622</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22400.4465088565</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24436.3476804049</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25887.4267893104</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28070.7671590431</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33140.3966580518</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39311.6686888272</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31232.273755865</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76888.7034353301</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75129.736201346</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71943.6819082981</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74391.7424466664</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79699.3420025909</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>85597.3689047616</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78862.9060889775</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78650.68713547</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88328.9210194286</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>100903.630138125</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110848.673332408</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>117717.02562963</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>139766.258050935</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>139731.587698751</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108621.399319824</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>423727.98384323</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>436045.208656843</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>443702.102450756</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>436524.608456385</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>462203.064439514</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>474106.932160748</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>444013.871894443</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>455376.646433438</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>505484.073342821</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>584439.607531008</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.627</t>
+          <t>626972.553838814</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>643284.312754908</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>718174.687319305</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>849738.459311631</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>696134.651238623</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>273996.821165837</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>268844.898076754</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>260909.302583487</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>251764.212399455</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>263648.899697703</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>288688.887001489</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>253089.902466675</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>272416.55078306</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>307091.951070079</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>377695.610205727</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>391254.966186911</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>419884.54750143</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>474372.128102749</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>529414.186827378</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>405161.691615154</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2.075</t>
+          <t>2074632.15060656</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.102</t>
+          <t>2101746.81502947</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2.116</t>
+          <t>2115355.26674224</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2.135</t>
+          <t>2134869.72741995</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.294</t>
+          <t>2299419.39914334</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2.478</t>
+          <t>2477596.53303171</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2.296</t>
+          <t>2294874.85809018</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2.256</t>
+          <t>2254754.60711442</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2.465</t>
+          <t>2465044.37071081</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2.871</t>
+          <t>2870304.1422716</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>3.176</t>
+          <t>3175864.31859751</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>3.408</t>
+          <t>3407166.13286583</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>3.725</t>
+          <t>3724279.91436067</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>4.089</t>
+          <t>4089793.63362713</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>3.195</t>
+          <t>3193888.80631782</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>17311416.2497018</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>17.881</t>
+          <t>17882090.9237241</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>18.299</t>
+          <t>18299541.2720699</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>18.483</t>
+          <t>18483360.2629244</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>19.277</t>
+          <t>19275115.528435</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>20.262</t>
+          <t>20262799.8877147</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20.415</t>
+          <t>20417175.1947568</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>21.716</t>
+          <t>21717918.6965316</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>24.238</t>
+          <t>24239009.2934183</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>27.537</t>
+          <t>27537667.7971602</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>30.307</t>
+          <t>30308282.9322417</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>33.105</t>
+          <t>33104520.7475083</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>37.265</t>
+          <t>37267742.6112281</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41731356.5418908</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>40.016</t>
+          <t>40015310.6390939</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>55.182</t>
+          <t>55182308.5366997</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>56.556</t>
+          <t>56556389.0503581</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>56.599</t>
+          <t>56598550.2992956</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>56.061</t>
+          <t>56060688.4328249</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>58.306</t>
+          <t>58306395.8341117</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>60.817</t>
+          <t>60817361.9019018</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>60.203</t>
+          <t>60202725.9733039</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>62.264</t>
+          <t>62263778.5854962</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>70.209</t>
+          <t>70209291.8668545</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>79.624</t>
+          <t>79623724.2735859</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>87.526</t>
+          <t>87525633.8786849</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>95.929</t>
+          <t>95929115.303749</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>109.398</t>
+          <t>109397506.893586</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>122.789</t>
+          <t>122789481.799157</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>114.158</t>
+          <t>114158105.32809</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gross_output.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
